--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260616.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260616.xlsx
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>168,841,000</t>
+          <t>885,744,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.31%</t>
+          <t>10.28%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>885,744,000</t>
+          <t>168,841,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.25%</t>
+          <t>10.03%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.44%</t>
+          <t>6.74%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.84%</t>
+          <t>4.81%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.31%</t>
+          <t>4.27%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>111,374,000</t>
+          <t>112,424,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.13%</t>
+          <t>4.06%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.73%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>3.28%</t>
         </is>
       </c>
     </row>
@@ -792,51 +792,51 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>134,180,945</t>
+          <t>28,485,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.91%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>28,485,000</t>
+          <t>134,180,945</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.90%</t>
         </is>
       </c>
     </row>
@@ -858,46 +858,46 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.86%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>93,188,442</t>
+          <t>144,292,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.66%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>144,292,000</t>
+          <t>93,188,442</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
@@ -1078,51 +1078,51 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.13%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>79,488,000</t>
+          <t>339,675,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>334,875,000</t>
+          <t>79,488,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.06%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>49,897,000</t>
+          <t>50,247,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,44 +1195,44 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>鈊  象</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>269,366,000</t>
+          <t>14,243,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>鈊  象</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>14,243,000</t>
+          <t>269,366,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>10,562,195,309</t>
+          <t>9,653,713,658</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>10,637,547,248</t>
+          <t>10,645,854,048</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-1,734,350,255</t>
+          <t>-1,998,118,917</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
